--- a/content/tz-kurs-po-razgovornoy-rechi-kitayskogo-yazyka.xlsx
+++ b/content/tz-kurs-po-razgovornoy-rechi-kitayskogo-yazyka.xlsx
@@ -20,6 +20,7 @@
     <sheet name="Ссылки" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Проверки" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="Оговорки" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Дополнение 11.09" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -531,7 +532,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Курс по разговорной речи китайского языка ищут, когда всё понимаешь, но не можешь ответить. Барьер здесь не про уровень: узнавать слово и доставать его в разговоре — разные навыки, и растут они по-разному. Разбираем, чем тон отличается от акцента и что из них правда важно, даём фразы для живого разговора и говорим, что должно быть в программе курса.</t>
+          <t>Курс по разговорной речи китайского языка ищут, когда всё понимаешь, но не можешь ответить. Барьер здесь не про уровень: узнавать слово и доставать его в разговоре — разные навыки. Разбираем, чем тон отличается от акцента, почему вы переводите в голове и как это проходит, какие фразы нужны в живом разговоре и что должно быть в программе курса устного китайского.</t>
         </is>
       </c>
     </row>
@@ -543,7 +544,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Почему барьер не про уровень языка, чем тон отличается от акцента, какие фразы нужны в живом разговоре и что должно быть в программе курса по разговорной речи китайского языка.</t>
+          <t>Почему барьер не про уровень языка, почему вы переводите в голове, чем тон отличается от акцента и что должно быть в программе курса устного китайского языка.</t>
         </is>
       </c>
     </row>
@@ -579,7 +580,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>10 сентября 2026</t>
+          <t>10 сентября 2026, дополнено 11 сентября</t>
         </is>
       </c>
     </row>
@@ -603,7 +604,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>37 286 знаков (лимит ≈ 50 000)</t>
+          <t>40 985 знаков (лимит ≈ 50 000)</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1101,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>37 286 знаков при лимите около 50 000</t>
+          <t>40 985 знаков при лимите около 50 000</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1149,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>вопросы и ответы совпадают, 6 из 6</t>
+          <t>вопросы и ответы совпадают, 7 из 7</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1233,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>34,8 % (читаемая часть кончается на 62,5 %)</t>
+          <t>29,8 % (читаемая часть кончается на 64,6 %)</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1245,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>38,7 %</t>
+          <t>33,0 %</t>
         </is>
       </c>
     </row>
@@ -1354,6 +1355,139 @@
       <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Не статистика, а описание конкретного студента из практики.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Дополнение от 11 сентября 2026: бриф «курс по устному китайскому»</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Что</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Как</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>ПОВОД</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Пришёл бриф «курс по устному китайскому языку». Это тот же интент, что у этой статьи: та же аудитория и те же обещания. Отдельная страница отобрала бы у этой трафик — поэтому её не делали, статью дополнили</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Что было новым</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Ровно один пункт: «строить фразы без перевода в голове». Проверено программно — в блоге нигде не разбиралось</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Новый H2</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>«Почему вы переводите в голове — и как это проходит»: таблица из четырёх причин с тем, что делать по каждой. Ключевая мысль: перевод включается там, где мысль сложнее уровня</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Новый вопрос в FAQ</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>«Как перестать переводить в голове?» — добавлен и в видимый блок, и в JSON-LD, слово в слово. Всего стало 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Вторичный ключ</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>«устный китайский» вписан в подводку, в заголовок H2 про программу и в дескрипшен; в тексте 9 вхождений</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>«На HSKK без заученных шаблонов»</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Закрыто отдельным абзацем и так, чтобы не противоречить нашему же разбору HSKK: клише-спасатели это не заученный ответ, а готовые куски, из которых ответ собирается на ходу</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Как правили</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Прямо в HTML, а не пересборкой: сборщик подставил бы локальные пути assets/ и стёр вписанные адреса картинок с Tilda. Адреса на месте, assets — ноль</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>ЧТО ДЕЛАТЬ В TILDA</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Блок перевставить заново и ОБНОВИТЬ ДЕСКРИПШЕН в настройках страницы — он изменился. Картинки не трогать, они те же</t>
         </is>
       </c>
     </row>
